--- a/salidas/empresas/PSX.xlsx
+++ b/salidas/empresas/PSX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B2" t="n">
-        <v>21.07632637023926</v>
+        <v>21.07633209228516</v>
       </c>
       <c r="C2" t="n">
         <v>34.04999923706055</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B3" t="n">
-        <v>18.5880184173584</v>
+        <v>18.5880241394043</v>
       </c>
       <c r="C3" t="n">
         <v>30.03000068664551</v>
@@ -526,11 +538,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B4" t="n">
-        <v>20.57496452331543</v>
+        <v>20.5749626159668</v>
       </c>
       <c r="C4" t="n">
         <v>33.2400016784668</v>
@@ -551,11 +563,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B5" t="n">
-        <v>23.39986038208008</v>
+        <v>23.39986228942871</v>
       </c>
       <c r="C5" t="n">
         <v>37.59999847412109</v>
@@ -576,11 +588,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B6" t="n">
-        <v>26.13814353942871</v>
+        <v>26.13812828063965</v>
       </c>
       <c r="C6" t="n">
         <v>42</v>
@@ -601,11 +613,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B7" t="n">
-        <v>28.85774803161621</v>
+        <v>28.85775184631348</v>
       </c>
       <c r="C7" t="n">
         <v>46.36999893188477</v>
@@ -626,11 +638,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B8" t="n">
-        <v>29.5128116607666</v>
+        <v>29.51281929016113</v>
       </c>
       <c r="C8" t="n">
         <v>47.15999984741211</v>
@@ -651,11 +663,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B9" t="n">
-        <v>32.77324676513672</v>
+        <v>32.77326202392578</v>
       </c>
       <c r="C9" t="n">
         <v>52.36999893188477</v>
@@ -676,11 +688,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B10" t="n">
-        <v>33.23006820678711</v>
+        <v>33.23007583618164</v>
       </c>
       <c r="C10" t="n">
         <v>53.09999847412109</v>
@@ -701,11 +713,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B11" t="n">
-        <v>37.90482330322266</v>
+        <v>37.90481185913086</v>
       </c>
       <c r="C11" t="n">
         <v>60.56999969482422</v>
@@ -726,11 +738,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B12" t="n">
-        <v>39.5936164855957</v>
+        <v>39.59361267089844</v>
       </c>
       <c r="C12" t="n">
         <v>62.95999908447266</v>
@@ -751,11 +763,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B13" t="n">
-        <v>44.00198364257812</v>
+        <v>44.00199127197266</v>
       </c>
       <c r="C13" t="n">
         <v>69.97000122070312</v>
@@ -776,11 +788,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B14" t="n">
-        <v>38.32958602905273</v>
+        <v>38.32957458496094</v>
       </c>
       <c r="C14" t="n">
         <v>60.95000076293945</v>
@@ -801,7 +813,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B15" t="n">
@@ -830,11 +842,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B16" t="n">
-        <v>37.22608184814453</v>
+        <v>37.2260856628418</v>
       </c>
       <c r="C16" t="n">
         <v>58.90999984741211</v>
@@ -859,11 +871,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B17" t="n">
-        <v>38.86273956298828</v>
+        <v>38.86274337768555</v>
       </c>
       <c r="C17" t="n">
         <v>61.5</v>
@@ -888,11 +900,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B18" t="n">
-        <v>36.27447891235352</v>
+        <v>36.27447509765625</v>
       </c>
       <c r="C18" t="n">
         <v>57.09999847412109</v>
@@ -917,11 +929,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B19" t="n">
-        <v>36.73186111450195</v>
+        <v>36.73186874389648</v>
       </c>
       <c r="C19" t="n">
         <v>57.81999969482422</v>
@@ -946,11 +958,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B20" t="n">
-        <v>40.93106842041016</v>
+        <v>40.93106079101562</v>
       </c>
       <c r="C20" t="n">
         <v>64.43000030517578</v>
@@ -975,11 +987,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B21" t="n">
-        <v>44.48674392700195</v>
+        <v>44.48674011230469</v>
       </c>
       <c r="C21" t="n">
         <v>69.61000061035156</v>
@@ -1004,11 +1016,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B22" t="n">
-        <v>49.29265213012695</v>
+        <v>49.29265594482422</v>
       </c>
       <c r="C22" t="n">
         <v>77.12999725341797</v>
@@ -1033,11 +1045,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B23" t="n">
-        <v>46.71075057983398</v>
+        <v>46.71075439453125</v>
       </c>
       <c r="C23" t="n">
         <v>73.08999633789062</v>
@@ -1062,11 +1074,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B24" t="n">
-        <v>48.09665679931641</v>
+        <v>48.09667205810547</v>
       </c>
       <c r="C24" t="n">
         <v>74.86000061035156</v>
@@ -1091,11 +1103,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B25" t="n">
-        <v>49.51015472412109</v>
+        <v>49.51012802124023</v>
       </c>
       <c r="C25" t="n">
         <v>77.05999755859375</v>
@@ -1120,11 +1132,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B26" t="n">
-        <v>53.46785354614258</v>
+        <v>53.46784973144531</v>
       </c>
       <c r="C26" t="n">
         <v>83.22000122070312</v>
@@ -1149,11 +1161,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B27" t="n">
-        <v>54.80450439453125</v>
+        <v>54.80451202392578</v>
       </c>
       <c r="C27" t="n">
         <v>84.79000091552734</v>
@@ -1178,11 +1190,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B28" t="n">
-        <v>51.98639678955078</v>
+        <v>51.98638916015625</v>
       </c>
       <c r="C28" t="n">
         <v>80.43000030517578</v>
@@ -1207,11 +1219,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B29" t="n">
-        <v>52.42589569091797</v>
+        <v>52.42592239379883</v>
       </c>
       <c r="C29" t="n">
         <v>81.11000061035156</v>
@@ -1236,7 +1248,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B30" t="n">
@@ -1265,11 +1277,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B31" t="n">
-        <v>52.87541198730469</v>
+        <v>52.87538909912109</v>
       </c>
       <c r="C31" t="n">
         <v>81.30999755859375</v>
@@ -1294,11 +1306,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B32" t="n">
-        <v>51.0480842590332</v>
+        <v>51.04807281494141</v>
       </c>
       <c r="C32" t="n">
         <v>78.5</v>
@@ -1323,11 +1335,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B33" t="n">
-        <v>47.80908966064453</v>
+        <v>47.80908203125</v>
       </c>
       <c r="C33" t="n">
         <v>73.01999664306641</v>
@@ -1352,11 +1364,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B34" t="n">
-        <v>46.94482040405273</v>
+        <v>46.94482803344727</v>
       </c>
       <c r="C34" t="n">
         <v>71.69999694824219</v>
@@ -1381,11 +1393,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B35" t="n">
-        <v>46.04128646850586</v>
+        <v>46.04127883911133</v>
       </c>
       <c r="C35" t="n">
         <v>70.31999969482422</v>
@@ -1410,11 +1422,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B36" t="n">
-        <v>51.71941375732422</v>
+        <v>51.71941757202148</v>
       </c>
       <c r="C36" t="n">
         <v>78.45999908447266</v>
@@ -1439,11 +1451,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B37" t="n">
-        <v>51.81171417236328</v>
+        <v>51.81170272827148</v>
       </c>
       <c r="C37" t="n">
         <v>78.59999847412109</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B38" t="n">
-        <v>52.27974319458008</v>
+        <v>52.27973175048828</v>
       </c>
       <c r="C38" t="n">
         <v>79.30999755859375</v>
@@ -1497,11 +1509,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B39" t="n">
-        <v>52.51861953735352</v>
+        <v>52.51861572265625</v>
       </c>
       <c r="C39" t="n">
         <v>79.12000274658203</v>
@@ -1526,7 +1538,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B40" t="n">
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B41" t="n">
-        <v>52.77085494995117</v>
+        <v>52.77084732055664</v>
       </c>
       <c r="C41" t="n">
         <v>79.5</v>
@@ -1584,11 +1596,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B42" t="n">
-        <v>52.83633422851562</v>
+        <v>52.83633041381836</v>
       </c>
       <c r="C42" t="n">
         <v>79.06999969482422</v>
@@ -1613,11 +1625,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B43" t="n">
-        <v>51.34618377685547</v>
+        <v>51.34620666503906</v>
       </c>
       <c r="C43" t="n">
         <v>76.83999633789062</v>
@@ -1642,11 +1654,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B44" t="n">
-        <v>59.50517654418945</v>
+        <v>59.50518798828125</v>
       </c>
       <c r="C44" t="n">
         <v>89.05000305175781</v>
@@ -1671,11 +1683,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B45" t="n">
-        <v>61.53691482543945</v>
+        <v>61.53689575195312</v>
       </c>
       <c r="C45" t="n">
         <v>91.52999877929688</v>
@@ -1700,11 +1712,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B46" t="n">
-        <v>54.99528884887695</v>
+        <v>54.99531173706055</v>
       </c>
       <c r="C46" t="n">
         <v>81.80000305175781</v>
@@ -1729,11 +1741,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B47" t="n">
-        <v>53.88599014282227</v>
+        <v>53.88596725463867</v>
       </c>
       <c r="C47" t="n">
         <v>80.15000152587891</v>
@@ -1758,11 +1770,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B48" t="n">
-        <v>53.77498245239258</v>
+        <v>53.77499008178711</v>
       </c>
       <c r="C48" t="n">
         <v>79.38999938964844</v>
@@ -1787,11 +1799,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B49" t="n">
-        <v>58.65190505981445</v>
+        <v>58.65192031860352</v>
       </c>
       <c r="C49" t="n">
         <v>86.58999633789062</v>
@@ -1816,11 +1828,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B50" t="n">
-        <v>55.61738967895508</v>
+        <v>55.61738586425781</v>
       </c>
       <c r="C50" t="n">
         <v>82.11000061035156</v>
@@ -1845,11 +1857,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B51" t="n">
-        <v>54.87331390380859</v>
+        <v>54.87329483032227</v>
       </c>
       <c r="C51" t="n">
         <v>80.36000061035156</v>
@@ -1874,11 +1886,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B52" t="n">
-        <v>54.17680740356445</v>
+        <v>54.17679977416992</v>
       </c>
       <c r="C52" t="n">
         <v>79.33999633789062</v>
@@ -1903,11 +1915,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B53" t="n">
-        <v>51.93705749511719</v>
+        <v>51.93707656860352</v>
       </c>
       <c r="C53" t="n">
         <v>76.05999755859375</v>
@@ -1932,11 +1944,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B54" t="n">
-        <v>54.00197982788086</v>
+        <v>54.0019645690918</v>
       </c>
       <c r="C54" t="n">
         <v>78.44999694824219</v>
@@ -1961,7 +1973,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B55" t="n">
@@ -1990,11 +2002,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B56" t="n">
-        <v>55.86055755615234</v>
+        <v>55.86054229736328</v>
       </c>
       <c r="C56" t="n">
         <v>81.15000152587891</v>
@@ -2019,11 +2031,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B57" t="n">
-        <v>57.62457275390625</v>
+        <v>57.62458038330078</v>
       </c>
       <c r="C57" t="n">
         <v>83.08000183105469</v>
@@ -2048,11 +2060,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B58" t="n">
-        <v>59.93429183959961</v>
+        <v>59.93428421020508</v>
       </c>
       <c r="C58" t="n">
         <v>86.41000366210938</v>
@@ -2077,11 +2089,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B59" t="n">
-        <v>56.61191177368164</v>
+        <v>56.6119270324707</v>
       </c>
       <c r="C59" t="n">
         <v>81.62000274658203</v>
@@ -2106,11 +2118,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B60" t="n">
-        <v>54.66290664672852</v>
+        <v>54.66289901733398</v>
       </c>
       <c r="C60" t="n">
         <v>78.19000244140625</v>
@@ -2135,11 +2147,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B61" t="n">
-        <v>55.38298034667969</v>
+        <v>55.38298416137695</v>
       </c>
       <c r="C61" t="n">
         <v>79.22000122070312</v>
@@ -2164,11 +2176,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B62" t="n">
-        <v>55.62067413330078</v>
+        <v>55.62068939208984</v>
       </c>
       <c r="C62" t="n">
         <v>79.55999755859375</v>
@@ -2193,11 +2205,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B63" t="n">
-        <v>53.67773818969727</v>
+        <v>53.677734375</v>
       </c>
       <c r="C63" t="n">
         <v>76.11000061035156</v>
@@ -2222,11 +2234,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B64" t="n">
-        <v>58.31839370727539</v>
+        <v>58.31838607788086</v>
       </c>
       <c r="C64" t="n">
         <v>82.69000244140625</v>
@@ -2251,11 +2263,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B65" t="n">
-        <v>59.06598281860352</v>
+        <v>59.06598663330078</v>
       </c>
       <c r="C65" t="n">
         <v>83.75</v>
@@ -2280,11 +2292,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B66" t="n">
-        <v>59.60691452026367</v>
+        <v>59.60689544677734</v>
       </c>
       <c r="C66" t="n">
         <v>83.80999755859375</v>
@@ -2309,11 +2321,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B67" t="n">
-        <v>65.15438079833984</v>
+        <v>65.15437316894531</v>
       </c>
       <c r="C67" t="n">
         <v>91.61000061035156</v>
@@ -2338,11 +2350,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B68" t="n">
-        <v>64.77744293212891</v>
+        <v>64.77745819091797</v>
       </c>
       <c r="C68" t="n">
         <v>91.08000183105469</v>
@@ -2367,11 +2379,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B69" t="n">
-        <v>69.91480255126953</v>
+        <v>69.91478729248047</v>
       </c>
       <c r="C69" t="n">
         <v>97.55999755859375</v>
@@ -2396,11 +2408,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B70" t="n">
-        <v>72.48752593994141</v>
+        <v>72.48753356933594</v>
       </c>
       <c r="C70" t="n">
         <v>101.1500015258789</v>
@@ -2425,11 +2437,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B71" t="n">
-        <v>73.38330841064453</v>
+        <v>73.38330078125</v>
       </c>
       <c r="C71" t="n">
         <v>102.4000015258789</v>
@@ -2454,7 +2466,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B72" t="n">
@@ -2483,11 +2495,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B73" t="n">
-        <v>69.26213836669922</v>
+        <v>69.26215362548828</v>
       </c>
       <c r="C73" t="n">
         <v>95.91999816894531</v>
@@ -2512,11 +2524,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B74" t="n">
-        <v>80.375</v>
+        <v>80.37498474121094</v>
       </c>
       <c r="C74" t="n">
         <v>111.3099975585938</v>
@@ -2541,11 +2553,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B75" t="n">
-        <v>84.67118835449219</v>
+        <v>84.67119598388672</v>
       </c>
       <c r="C75" t="n">
         <v>116.4899978637695</v>
@@ -2570,11 +2582,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B76" t="n">
-        <v>81.63294982910156</v>
+        <v>81.63294219970703</v>
       </c>
       <c r="C76" t="n">
         <v>112.3099975585938</v>
@@ -2599,11 +2611,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B77" t="n">
-        <v>89.650146484375</v>
+        <v>89.65013885498047</v>
       </c>
       <c r="C77" t="n">
         <v>123.3399963378906</v>
@@ -2628,11 +2640,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B78" t="n">
-        <v>86.74053192138672</v>
+        <v>86.74053955078125</v>
       </c>
       <c r="C78" t="n">
         <v>118.5100021362305</v>
@@ -2657,11 +2669,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B79" t="n">
-        <v>82.50270080566406</v>
+        <v>82.50272369384766</v>
       </c>
       <c r="C79" t="n">
         <v>112.7200012207031</v>
@@ -2686,7 +2698,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B80" t="n">
@@ -2715,11 +2727,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B81" t="n">
-        <v>69.02354431152344</v>
+        <v>69.02353668212891</v>
       </c>
       <c r="C81" t="n">
         <v>93.51999664306641</v>
@@ -2744,11 +2756,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B82" t="n">
-        <v>63.58402252197266</v>
+        <v>63.58403778076172</v>
       </c>
       <c r="C82" t="n">
         <v>86.15000152587891</v>
@@ -2773,7 +2785,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B83" t="n">
@@ -2802,11 +2814,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B84" t="n">
-        <v>71.71952056884766</v>
+        <v>71.71949005126953</v>
       </c>
       <c r="C84" t="n">
         <v>96.36000061035156</v>
@@ -2831,11 +2843,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B85" t="n">
-        <v>70.83379364013672</v>
+        <v>70.83378601074219</v>
       </c>
       <c r="C85" t="n">
         <v>95.16999816894531</v>
@@ -2860,11 +2872,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B86" t="n">
-        <v>70.16392517089844</v>
+        <v>70.16393280029297</v>
       </c>
       <c r="C86" t="n">
         <v>94.26999664306641</v>
@@ -2889,11 +2901,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B87" t="n">
-        <v>60.75765991210938</v>
+        <v>60.75766372680664</v>
       </c>
       <c r="C87" t="n">
         <v>80.80000305175781</v>
@@ -2918,11 +2930,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B88" t="n">
-        <v>70.33750152587891</v>
+        <v>70.33750915527344</v>
       </c>
       <c r="C88" t="n">
         <v>93.54000091552734</v>
@@ -2947,7 +2959,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B89" t="n">
@@ -2976,11 +2988,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B90" t="n">
-        <v>74.84654235839844</v>
+        <v>74.84653472900391</v>
       </c>
       <c r="C90" t="n">
         <v>98.62999725341797</v>
@@ -3005,11 +3017,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B91" t="n">
-        <v>77.70745086669922</v>
+        <v>77.70743560791016</v>
       </c>
       <c r="C91" t="n">
         <v>102.4000015258789</v>
@@ -3034,11 +3046,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B92" t="n">
-        <v>88.65023803710938</v>
+        <v>88.65021514892578</v>
       </c>
       <c r="C92" t="n">
         <v>116.8199996948242</v>
@@ -3063,11 +3075,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B93" t="n">
-        <v>87.71758270263672</v>
+        <v>87.71759033203125</v>
       </c>
       <c r="C93" t="n">
         <v>114.7200012207031</v>
@@ -3092,11 +3104,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B94" t="n">
-        <v>85.18668365478516</v>
+        <v>85.18667602539062</v>
       </c>
       <c r="C94" t="n">
         <v>111.4100036621094</v>
@@ -3121,11 +3133,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B95" t="n">
-        <v>69.86365509033203</v>
+        <v>69.8636474609375</v>
       </c>
       <c r="C95" t="n">
         <v>91.37000274658203</v>
@@ -3150,7 +3162,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B96" t="n">
@@ -3179,11 +3191,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B97" t="n">
-        <v>41.43483352661133</v>
+        <v>41.43483734130859</v>
       </c>
       <c r="C97" t="n">
         <v>53.65000152587891</v>
@@ -3208,11 +3220,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B98" t="n">
-        <v>56.51046752929688</v>
+        <v>56.51046371459961</v>
       </c>
       <c r="C98" t="n">
         <v>73.16999816894531</v>
@@ -3237,11 +3249,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B99" t="n">
-        <v>61.20934677124023</v>
+        <v>61.20934295654297</v>
       </c>
       <c r="C99" t="n">
         <v>78.26000213623047</v>
@@ -3266,11 +3278,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B100" t="n">
-        <v>56.23500823974609</v>
+        <v>56.23501586914062</v>
       </c>
       <c r="C100" t="n">
         <v>71.90000152587891</v>
@@ -3295,11 +3307,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B101" t="n">
-        <v>48.50758361816406</v>
+        <v>48.50759506225586</v>
       </c>
       <c r="C101" t="n">
         <v>62.02000045776367</v>
@@ -3322,11 +3334,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B102" t="n">
-        <v>46.38683319091797</v>
+        <v>46.38682556152344</v>
       </c>
       <c r="C102" t="n">
         <v>58.47000122070312</v>
@@ -3349,11 +3361,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B103" t="n">
-        <v>41.12696075439453</v>
+        <v>41.12697219848633</v>
       </c>
       <c r="C103" t="n">
         <v>51.84000015258789</v>
@@ -3376,11 +3388,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B104" t="n">
-        <v>37.01743698120117</v>
+        <v>37.01743316650391</v>
       </c>
       <c r="C104" t="n">
         <v>46.65999984741211</v>
@@ -3403,11 +3415,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B105" t="n">
-        <v>48.80835723876953</v>
+        <v>48.80836486816406</v>
       </c>
       <c r="C105" t="n">
         <v>60.58000183105469</v>
@@ -3430,11 +3442,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B106" t="n">
-        <v>56.34955978393555</v>
+        <v>56.34958267211914</v>
       </c>
       <c r="C106" t="n">
         <v>69.94000244140625</v>
@@ -3457,11 +3469,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B107" t="n">
-        <v>54.62541198730469</v>
+        <v>54.62540817260742</v>
       </c>
       <c r="C107" t="n">
         <v>67.80000305175781</v>
@@ -3484,7 +3496,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B108" t="n">
@@ -3511,11 +3523,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B109" t="n">
-        <v>66.44252014160156</v>
+        <v>66.44251251220703</v>
       </c>
       <c r="C109" t="n">
         <v>81.54000091552734</v>
@@ -3538,11 +3550,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B110" t="n">
-        <v>65.92917633056641</v>
+        <v>65.92918395996094</v>
       </c>
       <c r="C110" t="n">
         <v>80.91000366210938</v>
@@ -3565,11 +3577,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B111" t="n">
-        <v>69.35984802246094</v>
+        <v>69.35984039306641</v>
       </c>
       <c r="C111" t="n">
         <v>84.22000122070312</v>
@@ -3592,11 +3604,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B112" t="n">
-        <v>70.67752075195312</v>
+        <v>70.67751312255859</v>
       </c>
       <c r="C112" t="n">
         <v>85.81999969482422</v>
@@ -3619,11 +3631,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B113" t="n">
-        <v>60.47367858886719</v>
+        <v>60.47367095947266</v>
       </c>
       <c r="C113" t="n">
         <v>73.43000030517578</v>
@@ -3646,11 +3658,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B114" t="n">
-        <v>59.28922653198242</v>
+        <v>59.28921508789062</v>
       </c>
       <c r="C114" t="n">
         <v>71.08999633789062</v>
@@ -3673,7 +3685,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B115" t="n">
@@ -3700,11 +3712,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B116" t="n">
-        <v>62.36668395996094</v>
+        <v>62.36670684814453</v>
       </c>
       <c r="C116" t="n">
         <v>74.77999877929688</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B117" t="n">
-        <v>58.36843109130859</v>
+        <v>58.36843490600586</v>
       </c>
       <c r="C117" t="n">
         <v>69.16999816894531</v>
@@ -3754,11 +3766,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B118" t="n">
-        <v>61.14469146728516</v>
+        <v>61.14468002319336</v>
       </c>
       <c r="C118" t="n">
         <v>72.45999908447266</v>
@@ -3781,11 +3793,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B119" t="n">
-        <v>71.54922485351562</v>
+        <v>71.54924774169922</v>
       </c>
       <c r="C119" t="n">
         <v>84.79000091552734</v>
@@ -3808,7 +3820,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B120" t="n">
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B121" t="n">
-        <v>73.67813110351562</v>
+        <v>73.67814636230469</v>
       </c>
       <c r="C121" t="n">
         <v>86.38999938964844</v>
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B122" t="n">
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B123" t="n">
-        <v>86.86013031005859</v>
+        <v>86.86012268066406</v>
       </c>
       <c r="C123" t="n">
         <v>100.8099975585938</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B124" t="n">
-        <v>70.6444091796875</v>
+        <v>70.64440155029297</v>
       </c>
       <c r="C124" t="n">
         <v>81.98999786376953</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B125" t="n">
-        <v>76.68436431884766</v>
+        <v>76.68438720703125</v>
       </c>
       <c r="C125" t="n">
         <v>89</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B126" t="n">
-        <v>77.92661285400391</v>
+        <v>77.92659759521484</v>
       </c>
       <c r="C126" t="n">
         <v>89.45999908447266</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B127" t="n">
-        <v>70.31340026855469</v>
+        <v>70.31339263916016</v>
       </c>
       <c r="C127" t="n">
         <v>80.72000122070312</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B128" t="n">
-        <v>90.84468841552734</v>
+        <v>90.84468078613281</v>
       </c>
       <c r="C128" t="n">
         <v>104.2900009155273</v>
@@ -4069,7 +4081,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B129" t="n">
@@ -4098,7 +4110,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B130" t="n">
@@ -4127,7 +4139,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B131" t="n">
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B132" t="n">
-        <v>91.03556060791016</v>
+        <v>91.03557586669922</v>
       </c>
       <c r="C132" t="n">
         <v>102.5599975585938</v>
@@ -4185,7 +4197,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B133" t="n">
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B134" t="n">
-        <v>87.87560272216797</v>
+        <v>87.87559509277344</v>
       </c>
       <c r="C134" t="n">
         <v>99</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B135" t="n">
-        <v>82.21257781982422</v>
+        <v>82.21259307861328</v>
       </c>
       <c r="C135" t="n">
         <v>91.61000061035156</v>
@@ -4272,7 +4284,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B136" t="n">
@@ -4301,7 +4313,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B137" t="n">
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B138" t="n">
-        <v>103.4079818725586</v>
+        <v>103.4079895019531</v>
       </c>
       <c r="C138" t="n">
         <v>114.1600036621094</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B139" t="n">
-        <v>108.8338088989258</v>
+        <v>108.8338165283203</v>
       </c>
       <c r="C139" t="n">
         <v>120.1500015258789</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B140" t="n">
-        <v>103.3264389038086</v>
+        <v>103.3264312744141</v>
       </c>
       <c r="C140" t="n">
         <v>114.0699996948242</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B141" t="n">
-        <v>117.8218460083008</v>
+        <v>117.8218383789062</v>
       </c>
       <c r="C141" t="n">
         <v>128.8899993896484</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B142" t="n">
-        <v>121.7068786621094</v>
+        <v>121.7068710327148</v>
       </c>
       <c r="C142" t="n">
         <v>133.1399993896484</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B143" t="n">
-        <v>131.9176635742188</v>
+        <v>131.9176788330078</v>
       </c>
       <c r="C143" t="n">
         <v>144.3099975585938</v>
@@ -4504,7 +4516,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B144" t="n">
@@ -4533,7 +4545,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B145" t="n">
@@ -4562,7 +4574,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B146" t="n">
@@ -4591,7 +4603,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B147" t="n">
@@ -4620,7 +4632,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B148" t="n">
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B149" t="n">
-        <v>135.0126342773438</v>
+        <v>135.0126495361328</v>
       </c>
       <c r="C149" t="n">
         <v>145.4799957275391</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B150" t="n">
-        <v>131.2982482910156</v>
+        <v>131.2982788085938</v>
       </c>
       <c r="C150" t="n">
         <v>140.3099975585938</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B151" t="n">
-        <v>123.0073089599609</v>
+        <v>123.0073165893555</v>
       </c>
       <c r="C151" t="n">
         <v>131.4499969482422</v>
@@ -4736,7 +4748,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B152" t="n">
@@ -4765,7 +4777,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B153" t="n">
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B154" t="n">
-        <v>107.5574340820312</v>
+        <v>107.5574417114258</v>
       </c>
       <c r="C154" t="n">
         <v>113.9300003051758</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B155" t="n">
-        <v>111.2770462036133</v>
+        <v>111.2770614624023</v>
       </c>
       <c r="C155" t="n">
         <v>117.870002746582</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B156" t="n">
-        <v>123.5391159057617</v>
+        <v>123.5391006469727</v>
       </c>
       <c r="C156" t="n">
         <v>129.6900024414062</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B157" t="n">
-        <v>117.6236343383789</v>
+        <v>117.6236419677734</v>
       </c>
       <c r="C157" t="n">
         <v>123.4800033569336</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B158" t="n">
-        <v>99.12468719482422</v>
+        <v>99.12467956542969</v>
       </c>
       <c r="C158" t="n">
         <v>104.0599975585938</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B159" t="n">
-        <v>109.1395874023438</v>
+        <v>109.1395797729492</v>
       </c>
       <c r="C159" t="n">
         <v>113.4800033569336</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B160" t="n">
-        <v>114.7369613647461</v>
+        <v>114.7369689941406</v>
       </c>
       <c r="C160" t="n">
         <v>119.3000030517578</v>
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B161" t="n">
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B162" t="n">
-        <v>129.7381591796875</v>
+        <v>129.7381744384766</v>
       </c>
       <c r="C162" t="n">
         <v>133.5800018310547</v>
@@ -5055,7 +5067,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B163" t="n">
@@ -5084,7 +5096,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B164" t="n">
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B165" t="n">
-        <v>134.152099609375</v>
+        <v>134.1520843505859</v>
       </c>
       <c r="C165" t="n">
         <v>136.9600067138672</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B166" t="n">
-        <v>126.3944396972656</v>
+        <v>126.3944473266602</v>
       </c>
       <c r="C166" t="n">
         <v>129.0399932861328</v>
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B167" t="n">
-        <v>140.6167755126953</v>
+        <v>140.6167602539062</v>
       </c>
       <c r="C167" t="n">
         <v>143.5599975585938</v>
@@ -5200,7 +5212,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B168" t="n">
@@ -5229,7 +5241,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B169" t="n">
@@ -5258,7 +5270,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B170" t="n">
@@ -5287,7 +5299,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B171" t="n">
@@ -5316,7 +5328,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B172" t="n">
@@ -5345,7 +5357,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B173" t="n">
@@ -5374,7 +5386,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B174" t="n">
@@ -5403,32 +5415,32 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B175" t="n">
-        <v>256.4800109863281</v>
+        <v>255.8699951171875</v>
       </c>
       <c r="C175" t="n">
-        <v>256.4800109863281</v>
+        <v>255.8699951171875</v>
       </c>
       <c r="D175" t="n">
-        <v>55942300</v>
+        <v>58692900</v>
       </c>
       <c r="E175" t="n">
         <v>17.52</v>
       </c>
       <c r="F175" t="n">
-        <v>14.63927003346622</v>
+        <v>14.60445177609518</v>
       </c>
       <c r="G175" t="n">
         <v>399020916</v>
       </c>
       <c r="H175" t="n">
-        <v>102340888919.4547</v>
+        <v>102097479828.5757</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1401989162893907</v>
+        <v>0.1470922892673626</v>
       </c>
     </row>
   </sheetData>
@@ -5460,75 +5472,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5564,13 +5576,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5606,13 +5618,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5648,13 +5660,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5681,7 +5693,7 @@
       <c r="I5" t="n">
         <v>7.458700612153251</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K5" t="n">
@@ -5694,13 +5706,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5727,7 +5739,7 @@
       <c r="I6" t="n">
         <v>7.678700612153252</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K6" t="n">
@@ -5740,13 +5752,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5773,7 +5785,7 @@
       <c r="I7" t="n">
         <v>8.538700612153251</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K7" t="n">
@@ -5786,13 +5798,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5819,7 +5831,7 @@
       <c r="I8" t="n">
         <v>6.481871902306035</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K8" t="n">
@@ -5832,13 +5844,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5865,7 +5877,7 @@
       <c r="I9" t="n">
         <v>7.711871902306035</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K9" t="n">
@@ -5878,13 +5890,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5911,7 +5923,7 @@
       <c r="I10" t="n">
         <v>7.381871902306035</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="K10" t="n">
@@ -5924,13 +5936,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5957,7 +5969,7 @@
       <c r="I11" t="n">
         <v>5.741871902306035</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="K11" t="n">
@@ -5970,13 +5982,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6003,7 +6015,7 @@
       <c r="I12" t="n">
         <v>6.02</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K12" t="n">
@@ -6016,13 +6028,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6049,7 +6061,7 @@
       <c r="I13" t="n">
         <v>6.459999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K13" t="n">
@@ -6062,13 +6074,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6095,7 +6107,7 @@
       <c r="I14" t="n">
         <v>6.44</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K14" t="n">
@@ -6108,13 +6120,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6141,7 +6153,7 @@
       <c r="I15" t="n">
         <v>7.659999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K15" t="n">
@@ -6154,13 +6166,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6187,7 +6199,7 @@
       <c r="I16" t="n">
         <v>8.33</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K16" t="n">
@@ -6200,13 +6212,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6233,7 +6245,7 @@
       <c r="I17" t="n">
         <v>7.45</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K17" t="n">
@@ -6246,13 +6258,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6279,7 +6291,7 @@
       <c r="I18" t="n">
         <v>7.78</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="K18" t="n">
@@ -6292,13 +6304,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6325,7 +6337,7 @@
       <c r="I19" t="n">
         <v>8.59</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K19" t="n">
@@ -6338,13 +6350,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6371,7 +6383,7 @@
       <c r="I20" t="n">
         <v>7.730000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K20" t="n">
@@ -6384,13 +6396,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6417,7 +6429,7 @@
       <c r="I21" t="n">
         <v>6.660000000000001</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K21" t="n">
@@ -6430,13 +6442,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6463,7 +6475,7 @@
       <c r="I22" t="n">
         <v>5.750000000000002</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="K22" t="n">
@@ -6476,13 +6488,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6509,7 +6521,7 @@
       <c r="I23" t="n">
         <v>3.810000000000001</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K23" t="n">
@@ -6522,13 +6534,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6555,7 +6567,7 @@
       <c r="I24" t="n">
         <v>2.92</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="K24" t="n">
@@ -6568,13 +6580,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6601,7 +6613,7 @@
       <c r="I25" t="n">
         <v>3.22</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="K25" t="n">
@@ -6614,13 +6626,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6647,7 +6659,7 @@
       <c r="I26" t="n">
         <v>3.35</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="K26" t="n">
@@ -6660,13 +6672,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6693,7 +6705,7 @@
       <c r="I27" t="n">
         <v>3.99</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K27" t="n">
@@ -6706,13 +6718,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -6739,7 +6751,7 @@
       <c r="I28" t="n">
         <v>9.93</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K28" t="n">
@@ -6752,13 +6764,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -6785,7 +6797,7 @@
       <c r="I29" t="n">
         <v>9.98</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K29" t="n">
@@ -6798,13 +6810,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -6831,7 +6843,7 @@
       <c r="I30" t="n">
         <v>11.76</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K30" t="n">
@@ -6844,13 +6856,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -6877,7 +6889,7 @@
       <c r="I31" t="n">
         <v>13.34</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K31" t="n">
@@ -6890,13 +6902,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -6923,7 +6935,7 @@
       <c r="I32" t="n">
         <v>11.91</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K32" t="n">
@@ -6936,13 +6948,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -6969,7 +6981,7 @@
       <c r="I33" t="n">
         <v>11.28</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K33" t="n">
@@ -6982,13 +6994,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -7015,7 +7027,7 @@
       <c r="I34" t="n">
         <v>11.56</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K34" t="n">
@@ -7028,13 +7040,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7061,7 +7073,7 @@
       <c r="I35" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K35" t="n">
@@ -7074,13 +7086,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7107,7 +7119,7 @@
       <c r="I36" t="n">
         <v>6.78</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K36" t="n">
@@ -7120,13 +7132,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7153,7 +7165,7 @@
       <c r="I37" t="n">
         <v>0.6799999999999997</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K37" t="n">
@@ -7166,13 +7178,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7199,7 +7211,7 @@
       <c r="I38" t="n">
         <v>-2.77</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K38" t="n">
@@ -7212,13 +7224,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7245,7 +7257,7 @@
       <c r="I39" t="n">
         <v>-6.17</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K39" t="n">
@@ -7258,13 +7270,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7291,7 +7303,7 @@
       <c r="I40" t="n">
         <v>-9.040000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="K40" t="n">
@@ -7304,13 +7316,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7337,7 +7349,7 @@
       <c r="I41" t="n">
         <v>-4.87</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K41" t="n">
@@ -7350,13 +7362,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7383,7 +7395,7 @@
       <c r="I42" t="n">
         <v>-3.88</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K42" t="n">
@@ -7396,13 +7408,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7429,7 +7441,7 @@
       <c r="I43" t="n">
         <v>-1.15</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K43" t="n">
@@ -7442,13 +7454,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7475,7 +7487,7 @@
       <c r="I44" t="n">
         <v>2.97</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="K44" t="n">
@@ -7488,13 +7500,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7521,7 +7533,7 @@
       <c r="I45" t="n">
         <v>5.75</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K45" t="n">
@@ -7534,13 +7546,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7567,7 +7579,7 @@
       <c r="I46" t="n">
         <v>11.62</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K46" t="n">
@@ -7580,13 +7592,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -7613,7 +7625,7 @@
       <c r="I47" t="n">
         <v>21.87</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="K47" t="n">
@@ -7626,13 +7638,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -7659,7 +7671,7 @@
       <c r="I48" t="n">
         <v>23.27</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K48" t="n">
@@ -7672,13 +7684,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -7705,7 +7717,7 @@
       <c r="I49" t="n">
         <v>26.18</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K49" t="n">
@@ -7718,13 +7730,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -7751,7 +7763,7 @@
       <c r="I50" t="n">
         <v>23.37</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K50" t="n">
@@ -7764,13 +7776,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -7797,7 +7809,7 @@
       <c r="I51" t="n">
         <v>16.9</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K51" t="n">
@@ -7810,13 +7822,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -7843,7 +7855,7 @@
       <c r="I52" t="n">
         <v>15.48</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="K52" t="n">
@@ -7856,13 +7868,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -7889,7 +7901,7 @@
       <c r="I53" t="n">
         <v>13.01</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="K53" t="n">
@@ -7902,13 +7914,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -7935,7 +7947,7 @@
       <c r="I54" t="n">
         <v>11.67</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K54" t="n">
@@ -7948,13 +7960,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -7981,7 +7993,7 @@
       <c r="I55" t="n">
         <v>7.800000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="K55" t="n">
@@ -7994,13 +8006,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -8027,7 +8039,7 @@
       <c r="I56" t="n">
         <v>4.99</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K56" t="n">
@@ -8040,13 +8052,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -8073,7 +8085,7 @@
       <c r="I57" t="n">
         <v>4.44</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K57" t="n">
@@ -8086,13 +8098,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -8119,7 +8131,7 @@
       <c r="I58" t="n">
         <v>4.210000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="K58" t="n">
@@ -8132,13 +8144,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -8165,7 +8177,7 @@
       <c r="I59" t="n">
         <v>3.71</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="K59" t="n">
@@ -8178,13 +8190,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -8211,7 +8223,7 @@
       <c r="I60" t="n">
         <v>10.79</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="K60" t="n">
@@ -8224,13 +8236,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -8257,7 +8269,7 @@
       <c r="I61" t="n">
         <v>10.12</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K61" t="n">
@@ -8270,13 +8282,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -8303,7 +8315,7 @@
       <c r="I62" t="n">
         <v>17.52</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K62" t="n">
@@ -8340,52 +8352,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41045</v>
       </c>
       <c r="C2" t="n">
@@ -8414,10 +8426,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C3" t="n">
@@ -8446,10 +8458,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C4" t="n">
@@ -8478,10 +8490,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C5" t="n">
@@ -8510,10 +8522,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C6" t="n">
@@ -8542,10 +8554,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="C7" t="n">
@@ -8574,10 +8586,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="C8" t="n">
@@ -8606,10 +8618,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C9" t="n">
@@ -8638,10 +8650,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C10" t="n">
@@ -8670,10 +8682,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C11" t="n">
@@ -8702,10 +8714,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C12" t="n">
@@ -8734,10 +8746,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C13" t="n">
@@ -8766,10 +8778,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C14" t="n">
@@ -8798,10 +8810,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="C15" t="n">
@@ -8830,10 +8842,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C16" t="n">
@@ -8862,10 +8874,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C17" t="n">
@@ -8894,10 +8906,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C18" t="n">
@@ -8926,10 +8938,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="C19" t="n">
@@ -8958,10 +8970,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C20" t="n">
@@ -8990,10 +9002,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C21" t="n">
@@ -9022,10 +9034,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C22" t="n">
@@ -9054,10 +9066,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C23" t="n">
@@ -9086,10 +9098,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C24" t="n">
@@ -9118,10 +9130,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C25" t="n">
@@ -9150,10 +9162,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C26" t="n">
@@ -9182,10 +9194,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C27" t="n">
@@ -9214,10 +9226,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C28" t="n">
@@ -9246,10 +9258,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C29" t="n">
@@ -9278,10 +9290,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C30" t="n">
@@ -9310,10 +9322,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C31" t="n">
@@ -9342,10 +9354,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C32" t="n">
@@ -9374,10 +9386,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C33" t="n">
@@ -9406,10 +9418,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C34" t="n">
@@ -9438,10 +9450,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C35" t="n">
@@ -9470,10 +9482,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C36" t="n">
@@ -9502,10 +9514,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="C37" t="n">
@@ -9534,10 +9546,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C38" t="n">
@@ -9566,10 +9578,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C39" t="n">
@@ -9598,10 +9610,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C40" t="n">
@@ -9630,10 +9642,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="C41" t="n">
@@ -9662,10 +9674,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C42" t="n">
@@ -9694,10 +9706,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C43" t="n">
@@ -9726,10 +9738,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="C44" t="n">
@@ -9758,10 +9770,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="C45" t="n">
@@ -9790,10 +9802,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C46" t="n">
@@ -9822,10 +9834,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C47" t="n">
@@ -9854,10 +9866,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C48" t="n">
@@ -9886,10 +9898,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="C49" t="n">
@@ -9918,10 +9930,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="C50" t="n">
@@ -9950,10 +9962,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C51" t="n">
@@ -9982,10 +9994,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="C52" t="n">
@@ -10014,10 +10026,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C53" t="n">
@@ -10046,10 +10058,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C54" t="n">
@@ -10078,10 +10090,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="C55" t="n">
@@ -10110,10 +10122,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="C56" t="n">
@@ -10142,10 +10154,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="C57" t="n">
@@ -10174,10 +10186,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C58" t="n">
@@ -10206,10 +10218,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C59" t="n">
@@ -10256,12 +10268,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PSX.xlsx
+++ b/salidas/empresas/PSX.xlsx
@@ -517,7 +517,7 @@
         <v>41060</v>
       </c>
       <c r="B3" t="n">
-        <v>18.5880241394043</v>
+        <v>18.58802795410156</v>
       </c>
       <c r="C3" t="n">
         <v>30.03000068664551</v>
@@ -542,7 +542,7 @@
         <v>41090</v>
       </c>
       <c r="B4" t="n">
-        <v>20.5749626159668</v>
+        <v>20.57495498657227</v>
       </c>
       <c r="C4" t="n">
         <v>33.2400016784668</v>
@@ -567,7 +567,7 @@
         <v>41121</v>
       </c>
       <c r="B5" t="n">
-        <v>23.39986228942871</v>
+        <v>23.39986991882324</v>
       </c>
       <c r="C5" t="n">
         <v>37.59999847412109</v>
@@ -592,7 +592,7 @@
         <v>41152</v>
       </c>
       <c r="B6" t="n">
-        <v>26.13812828063965</v>
+        <v>26.13815116882324</v>
       </c>
       <c r="C6" t="n">
         <v>42</v>
@@ -617,7 +617,7 @@
         <v>41182</v>
       </c>
       <c r="B7" t="n">
-        <v>28.85775184631348</v>
+        <v>28.85774803161621</v>
       </c>
       <c r="C7" t="n">
         <v>46.36999893188477</v>
@@ -642,7 +642,7 @@
         <v>41213</v>
       </c>
       <c r="B8" t="n">
-        <v>29.51281929016113</v>
+        <v>29.51281356811523</v>
       </c>
       <c r="C8" t="n">
         <v>47.15999984741211</v>
@@ -667,7 +667,7 @@
         <v>41243</v>
       </c>
       <c r="B9" t="n">
-        <v>32.77326202392578</v>
+        <v>32.77323913574219</v>
       </c>
       <c r="C9" t="n">
         <v>52.36999893188477</v>
@@ -692,7 +692,7 @@
         <v>41274</v>
       </c>
       <c r="B10" t="n">
-        <v>33.23007583618164</v>
+        <v>33.23008728027344</v>
       </c>
       <c r="C10" t="n">
         <v>53.09999847412109</v>
@@ -717,7 +717,7 @@
         <v>41305</v>
       </c>
       <c r="B11" t="n">
-        <v>37.90481185913086</v>
+        <v>37.90482330322266</v>
       </c>
       <c r="C11" t="n">
         <v>60.56999969482422</v>
@@ -792,7 +792,7 @@
         <v>41394</v>
       </c>
       <c r="B14" t="n">
-        <v>38.32957458496094</v>
+        <v>38.32958984375</v>
       </c>
       <c r="C14" t="n">
         <v>60.95000076293945</v>
@@ -846,7 +846,7 @@
         <v>41455</v>
       </c>
       <c r="B16" t="n">
-        <v>37.2260856628418</v>
+        <v>37.22607803344727</v>
       </c>
       <c r="C16" t="n">
         <v>58.90999984741211</v>
@@ -875,7 +875,7 @@
         <v>41486</v>
       </c>
       <c r="B17" t="n">
-        <v>38.86274337768555</v>
+        <v>38.86275100708008</v>
       </c>
       <c r="C17" t="n">
         <v>61.5</v>
@@ -904,7 +904,7 @@
         <v>41517</v>
       </c>
       <c r="B18" t="n">
-        <v>36.27447509765625</v>
+        <v>36.27447128295898</v>
       </c>
       <c r="C18" t="n">
         <v>57.09999847412109</v>
@@ -933,7 +933,7 @@
         <v>41547</v>
       </c>
       <c r="B19" t="n">
-        <v>36.73186874389648</v>
+        <v>36.73186111450195</v>
       </c>
       <c r="C19" t="n">
         <v>57.81999969482422</v>
@@ -962,7 +962,7 @@
         <v>41578</v>
       </c>
       <c r="B20" t="n">
-        <v>40.93106079101562</v>
+        <v>40.93107604980469</v>
       </c>
       <c r="C20" t="n">
         <v>64.43000030517578</v>
@@ -991,7 +991,7 @@
         <v>41608</v>
       </c>
       <c r="B21" t="n">
-        <v>44.48674011230469</v>
+        <v>44.48674392700195</v>
       </c>
       <c r="C21" t="n">
         <v>69.61000061035156</v>
@@ -1020,7 +1020,7 @@
         <v>41639</v>
       </c>
       <c r="B22" t="n">
-        <v>49.29265594482422</v>
+        <v>49.29266738891602</v>
       </c>
       <c r="C22" t="n">
         <v>77.12999725341797</v>
@@ -1078,7 +1078,7 @@
         <v>41698</v>
       </c>
       <c r="B24" t="n">
-        <v>48.09667205810547</v>
+        <v>48.09664535522461</v>
       </c>
       <c r="C24" t="n">
         <v>74.86000061035156</v>
@@ -1136,7 +1136,7 @@
         <v>41759</v>
       </c>
       <c r="B26" t="n">
-        <v>53.46784973144531</v>
+        <v>53.46784210205078</v>
       </c>
       <c r="C26" t="n">
         <v>83.22000122070312</v>
@@ -1165,7 +1165,7 @@
         <v>41790</v>
       </c>
       <c r="B27" t="n">
-        <v>54.80451202392578</v>
+        <v>54.80451965332031</v>
       </c>
       <c r="C27" t="n">
         <v>84.79000091552734</v>
@@ -1252,7 +1252,7 @@
         <v>41882</v>
       </c>
       <c r="B30" t="n">
-        <v>56.58858108520508</v>
+        <v>56.58858871459961</v>
       </c>
       <c r="C30" t="n">
         <v>87.01999664306641</v>
@@ -1281,7 +1281,7 @@
         <v>41912</v>
       </c>
       <c r="B31" t="n">
-        <v>52.87538909912109</v>
+        <v>52.87539672851562</v>
       </c>
       <c r="C31" t="n">
         <v>81.30999755859375</v>
@@ -1310,7 +1310,7 @@
         <v>41943</v>
       </c>
       <c r="B32" t="n">
-        <v>51.04807281494141</v>
+        <v>51.04809188842773</v>
       </c>
       <c r="C32" t="n">
         <v>78.5</v>
@@ -1339,7 +1339,7 @@
         <v>41973</v>
       </c>
       <c r="B33" t="n">
-        <v>47.80908203125</v>
+        <v>47.8090705871582</v>
       </c>
       <c r="C33" t="n">
         <v>73.01999664306641</v>
@@ -1368,7 +1368,7 @@
         <v>42004</v>
       </c>
       <c r="B34" t="n">
-        <v>46.94482803344727</v>
+        <v>46.94482040405273</v>
       </c>
       <c r="C34" t="n">
         <v>71.69999694824219</v>
@@ -1397,7 +1397,7 @@
         <v>42035</v>
       </c>
       <c r="B35" t="n">
-        <v>46.04127883911133</v>
+        <v>46.04128646850586</v>
       </c>
       <c r="C35" t="n">
         <v>70.31999969482422</v>
@@ -1455,7 +1455,7 @@
         <v>42094</v>
       </c>
       <c r="B37" t="n">
-        <v>51.81170272827148</v>
+        <v>51.81171417236328</v>
       </c>
       <c r="C37" t="n">
         <v>78.59999847412109</v>
@@ -1484,7 +1484,7 @@
         <v>42124</v>
       </c>
       <c r="B38" t="n">
-        <v>52.27973175048828</v>
+        <v>52.27974319458008</v>
       </c>
       <c r="C38" t="n">
         <v>79.30999755859375</v>
@@ -1513,7 +1513,7 @@
         <v>42155</v>
       </c>
       <c r="B39" t="n">
-        <v>52.51861572265625</v>
+        <v>52.51861190795898</v>
       </c>
       <c r="C39" t="n">
         <v>79.12000274658203</v>
@@ -1542,7 +1542,7 @@
         <v>42185</v>
       </c>
       <c r="B40" t="n">
-        <v>53.47445297241211</v>
+        <v>53.47446823120117</v>
       </c>
       <c r="C40" t="n">
         <v>80.55999755859375</v>
@@ -1571,7 +1571,7 @@
         <v>42216</v>
       </c>
       <c r="B41" t="n">
-        <v>52.77084732055664</v>
+        <v>52.77084350585938</v>
       </c>
       <c r="C41" t="n">
         <v>79.5</v>
@@ -1600,7 +1600,7 @@
         <v>42247</v>
       </c>
       <c r="B42" t="n">
-        <v>52.83633041381836</v>
+        <v>52.83634185791016</v>
       </c>
       <c r="C42" t="n">
         <v>79.06999969482422</v>
@@ -1629,7 +1629,7 @@
         <v>42277</v>
       </c>
       <c r="B43" t="n">
-        <v>51.34620666503906</v>
+        <v>51.3462028503418</v>
       </c>
       <c r="C43" t="n">
         <v>76.83999633789062</v>
@@ -1658,7 +1658,7 @@
         <v>42308</v>
       </c>
       <c r="B44" t="n">
-        <v>59.50518798828125</v>
+        <v>59.50519180297852</v>
       </c>
       <c r="C44" t="n">
         <v>89.05000305175781</v>
@@ -1687,7 +1687,7 @@
         <v>42338</v>
       </c>
       <c r="B45" t="n">
-        <v>61.53689575195312</v>
+        <v>61.53691864013672</v>
       </c>
       <c r="C45" t="n">
         <v>91.52999877929688</v>
@@ -1716,7 +1716,7 @@
         <v>42369</v>
       </c>
       <c r="B46" t="n">
-        <v>54.99531173706055</v>
+        <v>54.99529647827148</v>
       </c>
       <c r="C46" t="n">
         <v>81.80000305175781</v>
@@ -1745,7 +1745,7 @@
         <v>42400</v>
       </c>
       <c r="B47" t="n">
-        <v>53.88596725463867</v>
+        <v>53.88599014282227</v>
       </c>
       <c r="C47" t="n">
         <v>80.15000152587891</v>
@@ -1774,7 +1774,7 @@
         <v>42429</v>
       </c>
       <c r="B48" t="n">
-        <v>53.77499008178711</v>
+        <v>53.77500152587891</v>
       </c>
       <c r="C48" t="n">
         <v>79.38999938964844</v>
@@ -1803,7 +1803,7 @@
         <v>42460</v>
       </c>
       <c r="B49" t="n">
-        <v>58.65192031860352</v>
+        <v>58.65193557739258</v>
       </c>
       <c r="C49" t="n">
         <v>86.58999633789062</v>
@@ -1832,7 +1832,7 @@
         <v>42490</v>
       </c>
       <c r="B50" t="n">
-        <v>55.61738586425781</v>
+        <v>55.61739730834961</v>
       </c>
       <c r="C50" t="n">
         <v>82.11000061035156</v>
@@ -1919,7 +1919,7 @@
         <v>42582</v>
       </c>
       <c r="B53" t="n">
-        <v>51.93707656860352</v>
+        <v>51.93706893920898</v>
       </c>
       <c r="C53" t="n">
         <v>76.05999755859375</v>
@@ -1948,7 +1948,7 @@
         <v>42613</v>
       </c>
       <c r="B54" t="n">
-        <v>54.0019645690918</v>
+        <v>54.00197601318359</v>
       </c>
       <c r="C54" t="n">
         <v>78.44999694824219</v>
@@ -1977,7 +1977,7 @@
         <v>42643</v>
       </c>
       <c r="B55" t="n">
-        <v>55.44754028320312</v>
+        <v>55.44752502441406</v>
       </c>
       <c r="C55" t="n">
         <v>80.55000305175781</v>
@@ -2035,7 +2035,7 @@
         <v>42704</v>
       </c>
       <c r="B57" t="n">
-        <v>57.62458038330078</v>
+        <v>57.62458801269531</v>
       </c>
       <c r="C57" t="n">
         <v>83.08000183105469</v>
@@ -2064,7 +2064,7 @@
         <v>42735</v>
       </c>
       <c r="B58" t="n">
-        <v>59.93428421020508</v>
+        <v>59.93428039550781</v>
       </c>
       <c r="C58" t="n">
         <v>86.41000366210938</v>
@@ -2093,7 +2093,7 @@
         <v>42766</v>
       </c>
       <c r="B59" t="n">
-        <v>56.6119270324707</v>
+        <v>56.61193084716797</v>
       </c>
       <c r="C59" t="n">
         <v>81.62000274658203</v>
@@ -2122,7 +2122,7 @@
         <v>42794</v>
       </c>
       <c r="B60" t="n">
-        <v>54.66289901733398</v>
+        <v>54.66290283203125</v>
       </c>
       <c r="C60" t="n">
         <v>78.19000244140625</v>
@@ -2180,7 +2180,7 @@
         <v>42855</v>
       </c>
       <c r="B62" t="n">
-        <v>55.62068939208984</v>
+        <v>55.62067794799805</v>
       </c>
       <c r="C62" t="n">
         <v>79.55999755859375</v>
@@ -2209,7 +2209,7 @@
         <v>42886</v>
       </c>
       <c r="B63" t="n">
-        <v>53.677734375</v>
+        <v>53.67774200439453</v>
       </c>
       <c r="C63" t="n">
         <v>76.11000061035156</v>
@@ -2238,7 +2238,7 @@
         <v>42916</v>
       </c>
       <c r="B64" t="n">
-        <v>58.31838607788086</v>
+        <v>58.31840133666992</v>
       </c>
       <c r="C64" t="n">
         <v>82.69000244140625</v>
@@ -2267,7 +2267,7 @@
         <v>42947</v>
       </c>
       <c r="B65" t="n">
-        <v>59.06598663330078</v>
+        <v>59.06596755981445</v>
       </c>
       <c r="C65" t="n">
         <v>83.75</v>
@@ -2296,7 +2296,7 @@
         <v>42978</v>
       </c>
       <c r="B66" t="n">
-        <v>59.60689544677734</v>
+        <v>59.6069221496582</v>
       </c>
       <c r="C66" t="n">
         <v>83.80999755859375</v>
@@ -2325,7 +2325,7 @@
         <v>43008</v>
       </c>
       <c r="B67" t="n">
-        <v>65.15437316894531</v>
+        <v>65.15438842773438</v>
       </c>
       <c r="C67" t="n">
         <v>91.61000061035156</v>
@@ -2354,7 +2354,7 @@
         <v>43039</v>
       </c>
       <c r="B68" t="n">
-        <v>64.77745819091797</v>
+        <v>64.77745056152344</v>
       </c>
       <c r="C68" t="n">
         <v>91.08000183105469</v>
@@ -2383,7 +2383,7 @@
         <v>43069</v>
       </c>
       <c r="B69" t="n">
-        <v>69.91478729248047</v>
+        <v>69.91481781005859</v>
       </c>
       <c r="C69" t="n">
         <v>97.55999755859375</v>
@@ -2412,7 +2412,7 @@
         <v>43100</v>
       </c>
       <c r="B70" t="n">
-        <v>72.48753356933594</v>
+        <v>72.48752593994141</v>
       </c>
       <c r="C70" t="n">
         <v>101.1500015258789</v>
@@ -2441,7 +2441,7 @@
         <v>43131</v>
       </c>
       <c r="B71" t="n">
-        <v>73.38330078125</v>
+        <v>73.38330841064453</v>
       </c>
       <c r="C71" t="n">
         <v>102.4000015258789</v>
@@ -2470,7 +2470,7 @@
         <v>43159</v>
       </c>
       <c r="B72" t="n">
-        <v>65.25458526611328</v>
+        <v>65.25459289550781</v>
       </c>
       <c r="C72" t="n">
         <v>90.37000274658203</v>
@@ -2499,7 +2499,7 @@
         <v>43190</v>
       </c>
       <c r="B73" t="n">
-        <v>69.26215362548828</v>
+        <v>69.26213836669922</v>
       </c>
       <c r="C73" t="n">
         <v>95.91999816894531</v>
@@ -2528,7 +2528,7 @@
         <v>43220</v>
       </c>
       <c r="B74" t="n">
-        <v>80.37498474121094</v>
+        <v>80.37499237060547</v>
       </c>
       <c r="C74" t="n">
         <v>111.3099975585938</v>
@@ -2557,7 +2557,7 @@
         <v>43251</v>
       </c>
       <c r="B75" t="n">
-        <v>84.67119598388672</v>
+        <v>84.67118072509766</v>
       </c>
       <c r="C75" t="n">
         <v>116.4899978637695</v>
@@ -2586,7 +2586,7 @@
         <v>43281</v>
       </c>
       <c r="B76" t="n">
-        <v>81.63294219970703</v>
+        <v>81.63294982910156</v>
       </c>
       <c r="C76" t="n">
         <v>112.3099975585938</v>
@@ -2615,7 +2615,7 @@
         <v>43312</v>
       </c>
       <c r="B77" t="n">
-        <v>89.65013885498047</v>
+        <v>89.650146484375</v>
       </c>
       <c r="C77" t="n">
         <v>123.3399963378906</v>
@@ -2644,7 +2644,7 @@
         <v>43343</v>
       </c>
       <c r="B78" t="n">
-        <v>86.74053955078125</v>
+        <v>86.74053192138672</v>
       </c>
       <c r="C78" t="n">
         <v>118.5100021362305</v>
@@ -2673,7 +2673,7 @@
         <v>43373</v>
       </c>
       <c r="B79" t="n">
-        <v>82.50272369384766</v>
+        <v>82.50267791748047</v>
       </c>
       <c r="C79" t="n">
         <v>112.7200012207031</v>
@@ -2702,7 +2702,7 @@
         <v>43404</v>
       </c>
       <c r="B80" t="n">
-        <v>75.25664520263672</v>
+        <v>75.25661468505859</v>
       </c>
       <c r="C80" t="n">
         <v>102.8199996948242</v>
@@ -2760,7 +2760,7 @@
         <v>43465</v>
       </c>
       <c r="B82" t="n">
-        <v>63.58403778076172</v>
+        <v>63.58401107788086</v>
       </c>
       <c r="C82" t="n">
         <v>86.15000152587891</v>
@@ -2789,7 +2789,7 @@
         <v>43496</v>
       </c>
       <c r="B83" t="n">
-        <v>70.41847991943359</v>
+        <v>70.41847229003906</v>
       </c>
       <c r="C83" t="n">
         <v>95.41000366210938</v>
@@ -2818,7 +2818,7 @@
         <v>43524</v>
       </c>
       <c r="B84" t="n">
-        <v>71.71949005126953</v>
+        <v>71.719482421875</v>
       </c>
       <c r="C84" t="n">
         <v>96.36000061035156</v>
@@ -2847,7 +2847,7 @@
         <v>43555</v>
       </c>
       <c r="B85" t="n">
-        <v>70.83378601074219</v>
+        <v>70.83377838134766</v>
       </c>
       <c r="C85" t="n">
         <v>95.16999816894531</v>
@@ -2876,7 +2876,7 @@
         <v>43585</v>
       </c>
       <c r="B86" t="n">
-        <v>70.16393280029297</v>
+        <v>70.16392517089844</v>
       </c>
       <c r="C86" t="n">
         <v>94.26999664306641</v>
@@ -2905,7 +2905,7 @@
         <v>43616</v>
       </c>
       <c r="B87" t="n">
-        <v>60.75766372680664</v>
+        <v>60.75765991210938</v>
       </c>
       <c r="C87" t="n">
         <v>80.80000305175781</v>
@@ -2963,7 +2963,7 @@
         <v>43677</v>
       </c>
       <c r="B89" t="n">
-        <v>77.12010955810547</v>
+        <v>77.12010192871094</v>
       </c>
       <c r="C89" t="n">
         <v>102.5599975585938</v>
@@ -2992,7 +2992,7 @@
         <v>43708</v>
       </c>
       <c r="B90" t="n">
-        <v>74.84653472900391</v>
+        <v>74.84652709960938</v>
       </c>
       <c r="C90" t="n">
         <v>98.62999725341797</v>
@@ -3021,7 +3021,7 @@
         <v>43738</v>
       </c>
       <c r="B91" t="n">
-        <v>77.70743560791016</v>
+        <v>77.70746612548828</v>
       </c>
       <c r="C91" t="n">
         <v>102.4000015258789</v>
@@ -3050,7 +3050,7 @@
         <v>43769</v>
       </c>
       <c r="B92" t="n">
-        <v>88.65021514892578</v>
+        <v>88.65023803710938</v>
       </c>
       <c r="C92" t="n">
         <v>116.8199996948242</v>
@@ -3108,7 +3108,7 @@
         <v>43830</v>
       </c>
       <c r="B94" t="n">
-        <v>85.18667602539062</v>
+        <v>85.18668365478516</v>
       </c>
       <c r="C94" t="n">
         <v>111.4100036621094</v>
@@ -3137,7 +3137,7 @@
         <v>43861</v>
       </c>
       <c r="B95" t="n">
-        <v>69.8636474609375</v>
+        <v>69.86363220214844</v>
       </c>
       <c r="C95" t="n">
         <v>91.37000274658203</v>
@@ -3166,7 +3166,7 @@
         <v>43890</v>
       </c>
       <c r="B96" t="n">
-        <v>57.81568145751953</v>
+        <v>57.81567764282227</v>
       </c>
       <c r="C96" t="n">
         <v>74.86000061035156</v>
@@ -3253,7 +3253,7 @@
         <v>43982</v>
       </c>
       <c r="B99" t="n">
-        <v>61.20934295654297</v>
+        <v>61.20934677124023</v>
       </c>
       <c r="C99" t="n">
         <v>78.26000213623047</v>
@@ -3282,7 +3282,7 @@
         <v>44012</v>
       </c>
       <c r="B100" t="n">
-        <v>56.23501586914062</v>
+        <v>56.23501205444336</v>
       </c>
       <c r="C100" t="n">
         <v>71.90000152587891</v>
@@ -3311,7 +3311,7 @@
         <v>44043</v>
       </c>
       <c r="B101" t="n">
-        <v>48.50759506225586</v>
+        <v>48.50758361816406</v>
       </c>
       <c r="C101" t="n">
         <v>62.02000045776367</v>
@@ -3338,7 +3338,7 @@
         <v>44074</v>
       </c>
       <c r="B102" t="n">
-        <v>46.38682556152344</v>
+        <v>46.3868293762207</v>
       </c>
       <c r="C102" t="n">
         <v>58.47000122070312</v>
@@ -3365,7 +3365,7 @@
         <v>44104</v>
       </c>
       <c r="B103" t="n">
-        <v>41.12697219848633</v>
+        <v>41.12694931030273</v>
       </c>
       <c r="C103" t="n">
         <v>51.84000015258789</v>
@@ -3392,7 +3392,7 @@
         <v>44135</v>
       </c>
       <c r="B104" t="n">
-        <v>37.01743316650391</v>
+        <v>37.01742935180664</v>
       </c>
       <c r="C104" t="n">
         <v>46.65999984741211</v>
@@ -3419,7 +3419,7 @@
         <v>44165</v>
       </c>
       <c r="B105" t="n">
-        <v>48.80836486816406</v>
+        <v>48.8083610534668</v>
       </c>
       <c r="C105" t="n">
         <v>60.58000183105469</v>
@@ -3446,7 +3446,7 @@
         <v>44196</v>
       </c>
       <c r="B106" t="n">
-        <v>56.34958267211914</v>
+        <v>56.34957504272461</v>
       </c>
       <c r="C106" t="n">
         <v>69.94000244140625</v>
@@ -3500,7 +3500,7 @@
         <v>44255</v>
       </c>
       <c r="B108" t="n">
-        <v>67.67293548583984</v>
+        <v>67.67292785644531</v>
       </c>
       <c r="C108" t="n">
         <v>83.05000305175781</v>
@@ -3554,7 +3554,7 @@
         <v>44316</v>
       </c>
       <c r="B110" t="n">
-        <v>65.92918395996094</v>
+        <v>65.92916870117188</v>
       </c>
       <c r="C110" t="n">
         <v>80.91000366210938</v>
@@ -3608,7 +3608,7 @@
         <v>44377</v>
       </c>
       <c r="B112" t="n">
-        <v>70.67751312255859</v>
+        <v>70.67750549316406</v>
       </c>
       <c r="C112" t="n">
         <v>85.81999969482422</v>
@@ -3635,7 +3635,7 @@
         <v>44408</v>
       </c>
       <c r="B113" t="n">
-        <v>60.47367095947266</v>
+        <v>60.47367477416992</v>
       </c>
       <c r="C113" t="n">
         <v>73.43000030517578</v>
@@ -3689,7 +3689,7 @@
         <v>44469</v>
       </c>
       <c r="B115" t="n">
-        <v>58.40517425537109</v>
+        <v>58.40518188476562</v>
       </c>
       <c r="C115" t="n">
         <v>70.02999877929688</v>
@@ -3716,7 +3716,7 @@
         <v>44500</v>
       </c>
       <c r="B116" t="n">
-        <v>62.36670684814453</v>
+        <v>62.3666877746582</v>
       </c>
       <c r="C116" t="n">
         <v>74.77999877929688</v>
@@ -3743,7 +3743,7 @@
         <v>44530</v>
       </c>
       <c r="B117" t="n">
-        <v>58.36843490600586</v>
+        <v>58.36845397949219</v>
       </c>
       <c r="C117" t="n">
         <v>69.16999816894531</v>
@@ -3797,7 +3797,7 @@
         <v>44592</v>
       </c>
       <c r="B119" t="n">
-        <v>71.54924774169922</v>
+        <v>71.54923248291016</v>
       </c>
       <c r="C119" t="n">
         <v>84.79000091552734</v>
@@ -3882,7 +3882,7 @@
         <v>44681</v>
       </c>
       <c r="B122" t="n">
-        <v>73.99370574951172</v>
+        <v>73.99368286132812</v>
       </c>
       <c r="C122" t="n">
         <v>86.76000213623047</v>
@@ -3911,7 +3911,7 @@
         <v>44712</v>
       </c>
       <c r="B123" t="n">
-        <v>86.86012268066406</v>
+        <v>86.86013793945312</v>
       </c>
       <c r="C123" t="n">
         <v>100.8099975585938</v>
@@ -3969,7 +3969,7 @@
         <v>44773</v>
       </c>
       <c r="B125" t="n">
-        <v>76.68438720703125</v>
+        <v>76.68436431884766</v>
       </c>
       <c r="C125" t="n">
         <v>89</v>
@@ -3998,7 +3998,7 @@
         <v>44804</v>
       </c>
       <c r="B126" t="n">
-        <v>77.92659759521484</v>
+        <v>77.92660522460938</v>
       </c>
       <c r="C126" t="n">
         <v>89.45999908447266</v>
@@ -4027,7 +4027,7 @@
         <v>44834</v>
       </c>
       <c r="B127" t="n">
-        <v>70.31339263916016</v>
+        <v>70.31338500976562</v>
       </c>
       <c r="C127" t="n">
         <v>80.72000122070312</v>
@@ -4085,7 +4085,7 @@
         <v>44895</v>
       </c>
       <c r="B129" t="n">
-        <v>95.29158020019531</v>
+        <v>95.29157257080078</v>
       </c>
       <c r="C129" t="n">
         <v>108.4400024414062</v>
@@ -4114,7 +4114,7 @@
         <v>44926</v>
       </c>
       <c r="B130" t="n">
-        <v>91.46023559570312</v>
+        <v>91.46025085449219</v>
       </c>
       <c r="C130" t="n">
         <v>104.0800018310547</v>
@@ -4143,7 +4143,7 @@
         <v>44957</v>
       </c>
       <c r="B131" t="n">
-        <v>88.11219024658203</v>
+        <v>88.1121826171875</v>
       </c>
       <c r="C131" t="n">
         <v>100.2699966430664</v>
@@ -4172,7 +4172,7 @@
         <v>44985</v>
       </c>
       <c r="B132" t="n">
-        <v>91.03557586669922</v>
+        <v>91.03556823730469</v>
       </c>
       <c r="C132" t="n">
         <v>102.5599975585938</v>
@@ -4201,7 +4201,7 @@
         <v>45016</v>
       </c>
       <c r="B133" t="n">
-        <v>89.98817443847656</v>
+        <v>89.98816680908203</v>
       </c>
       <c r="C133" t="n">
         <v>101.379997253418</v>
@@ -4259,7 +4259,7 @@
         <v>45077</v>
       </c>
       <c r="B135" t="n">
-        <v>82.21259307861328</v>
+        <v>82.21258544921875</v>
       </c>
       <c r="C135" t="n">
         <v>91.61000061035156</v>
@@ -4288,7 +4288,7 @@
         <v>45107</v>
       </c>
       <c r="B136" t="n">
-        <v>85.59585571289062</v>
+        <v>85.59584808349609</v>
       </c>
       <c r="C136" t="n">
         <v>95.37999725341797</v>
@@ -4346,7 +4346,7 @@
         <v>45169</v>
       </c>
       <c r="B138" t="n">
-        <v>103.4079895019531</v>
+        <v>103.4079666137695</v>
       </c>
       <c r="C138" t="n">
         <v>114.1600036621094</v>
@@ -4375,7 +4375,7 @@
         <v>45199</v>
       </c>
       <c r="B139" t="n">
-        <v>108.8338165283203</v>
+        <v>108.8338012695312</v>
       </c>
       <c r="C139" t="n">
         <v>120.1500015258789</v>
@@ -4404,7 +4404,7 @@
         <v>45230</v>
       </c>
       <c r="B140" t="n">
-        <v>103.3264312744141</v>
+        <v>103.3264541625977</v>
       </c>
       <c r="C140" t="n">
         <v>114.0699996948242</v>
@@ -4462,7 +4462,7 @@
         <v>45291</v>
       </c>
       <c r="B142" t="n">
-        <v>121.7068710327148</v>
+        <v>121.7068862915039</v>
       </c>
       <c r="C142" t="n">
         <v>133.1399993896484</v>
@@ -4491,7 +4491,7 @@
         <v>45322</v>
       </c>
       <c r="B143" t="n">
-        <v>131.9176788330078</v>
+        <v>131.9177093505859</v>
       </c>
       <c r="C143" t="n">
         <v>144.3099975585938</v>
@@ -4520,7 +4520,7 @@
         <v>45351</v>
       </c>
       <c r="B144" t="n">
-        <v>131.2135162353516</v>
+        <v>131.2135314941406</v>
       </c>
       <c r="C144" t="n">
         <v>142.5099945068359</v>
@@ -4549,7 +4549,7 @@
         <v>45382</v>
       </c>
       <c r="B145" t="n">
-        <v>150.3923645019531</v>
+        <v>150.3923797607422</v>
       </c>
       <c r="C145" t="n">
         <v>163.3399963378906</v>
@@ -4578,7 +4578,7 @@
         <v>45412</v>
       </c>
       <c r="B146" t="n">
-        <v>131.8580322265625</v>
+        <v>131.8580474853516</v>
       </c>
       <c r="C146" t="n">
         <v>143.2100067138672</v>
@@ -4607,7 +4607,7 @@
         <v>45443</v>
       </c>
       <c r="B147" t="n">
-        <v>131.8851318359375</v>
+        <v>131.8851165771484</v>
       </c>
       <c r="C147" t="n">
         <v>142.1100006103516</v>
@@ -4636,7 +4636,7 @@
         <v>45473</v>
       </c>
       <c r="B148" t="n">
-        <v>131.0127563476562</v>
+        <v>131.0127410888672</v>
       </c>
       <c r="C148" t="n">
         <v>141.1699981689453</v>
@@ -4665,7 +4665,7 @@
         <v>45504</v>
       </c>
       <c r="B149" t="n">
-        <v>135.0126495361328</v>
+        <v>135.0126647949219</v>
       </c>
       <c r="C149" t="n">
         <v>145.4799957275391</v>
@@ -4694,7 +4694,7 @@
         <v>45535</v>
       </c>
       <c r="B150" t="n">
-        <v>131.2982788085938</v>
+        <v>131.2982635498047</v>
       </c>
       <c r="C150" t="n">
         <v>140.3099975585938</v>
@@ -4781,7 +4781,7 @@
         <v>45626</v>
       </c>
       <c r="B153" t="n">
-        <v>126.4859466552734</v>
+        <v>126.4859619140625</v>
       </c>
       <c r="C153" t="n">
         <v>133.9799957275391</v>
@@ -4810,7 +4810,7 @@
         <v>45657</v>
       </c>
       <c r="B154" t="n">
-        <v>107.5574417114258</v>
+        <v>107.5574264526367</v>
       </c>
       <c r="C154" t="n">
         <v>113.9300003051758</v>
@@ -4868,7 +4868,7 @@
         <v>45716</v>
       </c>
       <c r="B156" t="n">
-        <v>123.5391006469727</v>
+        <v>123.5391235351562</v>
       </c>
       <c r="C156" t="n">
         <v>129.6900024414062</v>
@@ -4897,7 +4897,7 @@
         <v>45747</v>
       </c>
       <c r="B157" t="n">
-        <v>117.6236419677734</v>
+        <v>117.6236343383789</v>
       </c>
       <c r="C157" t="n">
         <v>123.4800033569336</v>
@@ -5013,7 +5013,7 @@
         <v>45869</v>
       </c>
       <c r="B161" t="n">
-        <v>118.8532638549805</v>
+        <v>118.8532562255859</v>
       </c>
       <c r="C161" t="n">
         <v>123.5800018310547</v>
@@ -5158,7 +5158,7 @@
         <v>46022</v>
       </c>
       <c r="B166" t="n">
-        <v>126.3944473266602</v>
+        <v>126.3944396972656</v>
       </c>
       <c r="C166" t="n">
         <v>129.0399932861328</v>
@@ -5187,7 +5187,7 @@
         <v>46053</v>
       </c>
       <c r="B167" t="n">
-        <v>140.6167602539062</v>
+        <v>140.6167755126953</v>
       </c>
       <c r="C167" t="n">
         <v>143.5599975585938</v>
